--- a/artfynd/A 68433-2021 artfynd.xlsx
+++ b/artfynd/A 68433-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68433-2021 artfynd.xlsx
+++ b/artfynd/A 68433-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>165109</v>
       </c>
       <c r="B2" t="n">
-        <v>85702</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454773.9709753319</v>
+        <v>454774</v>
       </c>
       <c r="R2" t="n">
-        <v>6925935.156715738</v>
+        <v>6925935</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,12 +792,7 @@
         <v>87967120</v>
       </c>
       <c r="B3" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455068.8357789813</v>
+        <v>455069</v>
       </c>
       <c r="R3" t="n">
-        <v>6926013.07641949</v>
+        <v>6926013</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +860,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,12 +893,7 @@
         <v>87967123</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455068.8357789813</v>
+        <v>455069</v>
       </c>
       <c r="R4" t="n">
-        <v>6926013.07641949</v>
+        <v>6926013</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,19 +961,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87967144</v>
+        <v>87967133</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455014.8470228538</v>
+        <v>455049</v>
       </c>
       <c r="R5" t="n">
-        <v>6926133.192498556</v>
+        <v>6926041</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,19 +1062,9 @@
           <t>2020-09-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,6 +1089,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87967144</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åsmyrvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>455015</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6926133</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68433-2021 artfynd.xlsx
+++ b/artfynd/A 68433-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/165109</t>
         </is>
       </c>
     </row>
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87967120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87967123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87967133</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,8 +1215,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87967144</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>